--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,14 +781,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91349</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +882,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128090</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127128087</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34727-2025 artfynd.xlsx
+++ b/artfynd/A 34727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128087</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128090</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>